--- a/results/job_matches_2026-05-03.xlsx
+++ b/results/job_matches_2026-05-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,77 +538,77 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>DevOps Engineer Live Streaming- Wixom, MI</t>
+          <t>Sr. Software Engineer - AI Engineering and Productivity</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>J&amp;B Medical</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Wixom, MI, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, Athena, Step Functions, S3, RDS, Azure, GCP, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=823e57252a5543a0</t>
+          <t>https://www.indeed.com/viewjob?jk=678daaae3aea7ce1</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - AI Engineering and Productivity</t>
+          <t>Senior DevOps Engineer (GCP)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, SQL Server, PostgreSQL</t>
+          <t>Azure, Google Cloud Platform, GCP, Kafka, NoSQL, Data Modeling, ETL, Talend, Tableau, Splunk</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=678daaae3aea7ce1</t>
+          <t>https://www.indeed.com/viewjob?jk=abcb767c36c64a35</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer (GCP)</t>
+          <t>Cloud AI Application Administrator</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -622,11 +622,11 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16</v>
+        <v>13.9</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Azure, Google Cloud Platform, GCP, Kafka, NoSQL, Data Modeling, ETL, Talend, Tableau, Splunk</t>
+          <t>AWS, Lambda, S3, ECS, IAM, Azure, Scala, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,67 +636,67 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abcb767c36c64a35</t>
+          <t>https://www.indeed.com/viewjob?jk=18ebfd30511cd60d</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Cloud / DevOps Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Toyota North America</t>
+          <t>RHP Properties</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Farmington Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=616b27159c04b0d8</t>
+          <t>https://www.indeed.com/viewjob?jk=3d8ec5a3c163d85b</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Cloud AI Application Administrator</t>
+          <t>Software Engineer III - PySpark/AWS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, Azure, Scala, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18ebfd30511cd60d</t>
+          <t>https://www.indeed.com/viewjob?jk=ee6714b6afaed3b1</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>GCP Support Associate</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>RHP Properties</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Farmington Hills, MI, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, EMR, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d8ec5a3c163d85b</t>
+          <t>https://www.indeed.com/viewjob?jk=0d636a662e603c9d</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Associate Data &amp; Analytics Engineer</t>
+          <t>Data Engineer - Microsoft Fabric</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Clinical Care Options LLC</t>
+          <t>Provoke Solutions</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark, PySpark, Scala, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Unity Catalog, Spark, PySpark, Scala, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13564543da011952</t>
+          <t>https://www.indeed.com/viewjob?jk=3b922fcc276be07d</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Software Engineer III - PySpark/AWS</t>
+          <t>GCP Support Associate</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Databricks, Spark, PySpark</t>
+          <t>ECS, IAM, Google Cloud Platform, GCP, Dataflow, Cloud Storage, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,14 +811,14 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee6714b6afaed3b1</t>
+          <t>https://www.indeed.com/viewjob?jk=1097e9f29f6e8b0a</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>GCP Support Associate</t>
+          <t>Junior GCP Cloud Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -832,11 +832,11 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, EMR, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Snowflake</t>
+          <t>ECS, IAM, Google Cloud Platform, GCP, Dataflow, Cloud Storage, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d636a662e603c9d</t>
+          <t>https://www.indeed.com/viewjob?jk=08d4cd78d3dbe405</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, MLOps, MLflow, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=011200ffdfb2dd05</t>
+          <t>https://www.indeed.com/viewjob?jk=393116d7c03fb80f</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer - Microsoft Fabric</t>
+          <t>Software Development Engineer in Test (SDET)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Provoke Solutions</t>
+          <t>Foodsmart</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>West, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Unity Catalog, Spark, PySpark, Scala, ELT, dbt, Power BI</t>
+          <t>AWS, Redshift, S3, RDS, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b922fcc276be07d</t>
+          <t>https://www.indeed.com/viewjob?jk=1ff1351b933e73ff</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>GCP Support Associate</t>
+          <t>Software Development Engineer in Test (SDET)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Foodsmart</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,34 +941,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ECS, IAM, Google Cloud Platform, GCP, Dataflow, Cloud Storage, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, Redshift, S3, RDS, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1097e9f29f6e8b0a</t>
+          <t>https://www.indeed.com/viewjob?jk=547c7125b0b30619</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Junior GCP Cloud Engineer</t>
+          <t>Software Development Engineer in Test (SDET)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Foodsmart</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,59 +976,59 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ECS, IAM, Google Cloud Platform, GCP, Dataflow, Cloud Storage, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, Redshift, S3, RDS, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08d4cd78d3dbe405</t>
+          <t>https://www.indeed.com/viewjob?jk=364f3e4259c47f25</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Foodsmart</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, MLOps, MLflow, CI/CD, Jenkins, Docker</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=393116d7c03fb80f</t>
+          <t>https://www.indeed.com/viewjob?jk=aaeba0c578886154</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1038,15 +1038,15 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>West, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,14 +1056,14 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ff1351b933e73ff</t>
+          <t>https://www.indeed.com/viewjob?jk=1c32c34ff06b9605</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1073,15 +1073,15 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>West, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,164 +1091,164 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=547c7125b0b30619</t>
+          <t>https://www.indeed.com/viewjob?jk=9c0f59a5cadbe7f1</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET)</t>
+          <t>Data Modeling &amp; Data Governance Senior Consultant - Global Employer Services Technology</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Foodsmart</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
+          <t>Redshift, RDS, Databricks, Scala, Snowflake, Oracle, Data Modeling, Snowflake Schema, ELT, Git</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=364f3e4259c47f25</t>
+          <t>https://www.indeed.com/viewjob?jk=b5bbdd9aeeabb621</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Modeling &amp; Data Governance Senior Consultant - Global Employer Services Technology</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Foodsmart</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, Airflow, Apache Airflow</t>
+          <t>Redshift, RDS, Databricks, Scala, Snowflake, Oracle, Data Modeling, Snowflake Schema, ELT, Git</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aaeba0c578886154</t>
+          <t>https://www.indeed.com/viewjob?jk=c86ac4ab76e539c1</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Modeling &amp; Data Governance Senior Consultant - Global Employer Services Technology</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Foodsmart</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, Airflow, Apache Airflow</t>
+          <t>Redshift, RDS, Databricks, Scala, Snowflake, Oracle, Data Modeling, Snowflake Schema, ELT, Git</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c32c34ff06b9605</t>
+          <t>https://www.indeed.com/viewjob?jk=06a961338cdff4c7</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Modeling &amp; Data Governance Senior Consultant - Global Employer Services Technology</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Foodsmart</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>West, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, Airflow, Apache Airflow</t>
+          <t>Redshift, RDS, Databricks, Scala, Snowflake, Oracle, Data Modeling, Snowflake Schema, ELT, Git</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c0f59a5cadbe7f1</t>
+          <t>https://www.indeed.com/viewjob?jk=5a8dc52df424a812</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
+          <t>Data Modeling &amp; Data Governance Senior Consultant - Global Employer Services Technology</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>Redshift, RDS, Databricks, Scala, Snowflake, Oracle, Data Modeling, Snowflake Schema, ELT, Git</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b221a3fa0ea5bd27</t>
+          <t>https://www.indeed.com/viewjob?jk=3e3d3e1280702eb1</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
+          <t>Data Modeling &amp; Data Governance Senior Consultant - Global Employer Services Technology</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>Redshift, RDS, Databricks, Scala, Snowflake, Oracle, Data Modeling, Snowflake Schema, ELT, Git</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,40 +1301,530 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc63a267293974cf</t>
+          <t>https://www.indeed.com/viewjob?jk=61ce98159d51d115</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>Data Modeling &amp; Data Governance Senior Consultant - Global Employer Services Technology</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Redshift, RDS, Databricks, Scala, Snowflake, Oracle, Data Modeling, Snowflake Schema, ELT, Git</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e949ea802386aee4</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Data Modeling &amp; Data Governance Senior Consultant - Global Employer Services Technology</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Redshift, RDS, Databricks, Scala, Snowflake, Oracle, Data Modeling, Snowflake Schema, ELT, Git</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=89b2dfb0f97e69c0</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Data Modeling &amp; Data Governance Senior Consultant - Global Employer Services Technology</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Jacksonville, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Redshift, RDS, Databricks, Scala, Snowflake, Oracle, Data Modeling, Snowflake Schema, ELT, Git</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5426946ff66f44cb</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Data Modeling &amp; Data Governance Senior Consultant - Global Employer Services Technology</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>San Diego, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Redshift, RDS, Databricks, Scala, Snowflake, Oracle, Data Modeling, Snowflake Schema, ELT, Git</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=966efb03a4505663</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Data Modeling &amp; Data Governance Senior Consultant - Global Employer Services Technology</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Redshift, RDS, Databricks, Scala, Snowflake, Oracle, Data Modeling, Snowflake Schema, ELT, Git</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9cd0270d6d2fdb49</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Data Modeling &amp; Data Governance Senior Consultant - Global Employer Services Technology</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Redshift, RDS, Databricks, Scala, Snowflake, Oracle, Data Modeling, Snowflake Schema, ELT, Git</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=79d317ebbe4365ed</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Data Modeling &amp; Data Governance Senior Consultant - Global Employer Services Technology</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Jersey City, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Redshift, RDS, Databricks, Scala, Snowflake, Oracle, Data Modeling, Snowflake Schema, ELT, Git</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=aa85be0d893f7e04</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Data Modeling &amp; Data Governance Senior Consultant - Global Employer Services Technology</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Redshift, RDS, Databricks, Scala, Snowflake, Oracle, Data Modeling, Snowflake Schema, ELT, Git</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d0728d5f76d49bf4</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Data Modeling &amp; Data Governance Senior Consultant - Global Employer Services Technology</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Redshift, RDS, Databricks, Scala, Snowflake, Oracle, Data Modeling, Snowflake Schema, ELT, Git</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1336edda4057fc25</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Data Modeling &amp; Data Governance Senior Consultant - Global Employer Services Technology</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Redshift, RDS, Databricks, Scala, Snowflake, Oracle, Data Modeling, Snowflake Schema, ELT, Git</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=793c1866762fa2ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Data Modeling &amp; Data Governance Senior Consultant - Global Employer Services Technology</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Redshift, RDS, Databricks, Scala, Snowflake, Oracle, Data Modeling, Snowflake Schema, ELT, Git</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4df1d967651bceda</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Data Modeling &amp; Data Governance Senior Consultant - Global Employer Services Technology</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Costa Mesa, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Redshift, RDS, Databricks, Scala, Snowflake, Oracle, Data Modeling, Snowflake Schema, ELT, Git</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8e3288bd3db664fa</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Bethesda, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b221a3fa0ea5bd27</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cc63a267293974cf</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
           <t>AI Application Architect</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>Openkyber</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>AK, US USA</t>
         </is>
       </c>
-      <c r="D26" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E26" t="inlineStr">
+      <c r="D40" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E40" t="inlineStr">
         <is>
           <t>AWS, Azure, Google Cloud Platform, Spark, Scala, Snowflake, ETL, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=b57504d4cd793d31</t>
         </is>

--- a/results/job_matches_2026-05-03.xlsx
+++ b/results/job_matches_2026-05-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G40"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,25 +643,25 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Software Engineer III - PySpark/AWS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>RHP Properties</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Farmington Hills, MI, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d8ec5a3c163d85b</t>
+          <t>https://www.indeed.com/viewjob?jk=ee6714b6afaed3b1</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Software Engineer III - PySpark/AWS</t>
+          <t>GCP Support Associate</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Databricks, Spark, PySpark</t>
+          <t>AWS, EMR, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee6714b6afaed3b1</t>
+          <t>https://www.indeed.com/viewjob?jk=0d636a662e603c9d</t>
         </is>
       </c>
     </row>
@@ -727,11 +727,11 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, EMR, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Snowflake</t>
+          <t>ECS, IAM, Google Cloud Platform, GCP, Dataflow, Cloud Storage, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,49 +741,49 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d636a662e603c9d</t>
+          <t>https://www.indeed.com/viewjob?jk=1097e9f29f6e8b0a</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer - Microsoft Fabric</t>
+          <t>Junior GCP Cloud Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Provoke Solutions</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Unity Catalog, Spark, PySpark, Scala, ELT, dbt, Power BI</t>
+          <t>ECS, IAM, Google Cloud Platform, GCP, Dataflow, Cloud Storage, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b922fcc276be07d</t>
+          <t>https://www.indeed.com/viewjob?jk=08d4cd78d3dbe405</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>GCP Support Associate</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ECS, IAM, Google Cloud Platform, GCP, Dataflow, Cloud Storage, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, MLOps, MLflow, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1097e9f29f6e8b0a</t>
+          <t>https://www.indeed.com/viewjob?jk=393116d7c03fb80f</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Junior GCP Cloud Engineer</t>
+          <t>Data Modeling &amp; Data Governance Senior Consultant - Global Employer Services Technology</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ECS, IAM, Google Cloud Platform, GCP, Dataflow, Cloud Storage, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>Redshift, RDS, Databricks, Scala, Snowflake, Oracle, Data Modeling, Snowflake Schema, ELT, Git</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08d4cd78d3dbe405</t>
+          <t>https://www.indeed.com/viewjob?jk=b5bbdd9aeeabb621</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Data Modeling &amp; Data Governance Senior Consultant - Global Employer Services Technology</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, MLOps, MLflow, CI/CD, Jenkins, Docker</t>
+          <t>Redshift, RDS, Databricks, Scala, Snowflake, Oracle, Data Modeling, Snowflake Schema, ELT, Git</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,217 +881,217 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=393116d7c03fb80f</t>
+          <t>https://www.indeed.com/viewjob?jk=c86ac4ab76e539c1</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET)</t>
+          <t>Data Modeling &amp; Data Governance Senior Consultant - Global Employer Services Technology</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Foodsmart</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>West, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
+          <t>Redshift, RDS, Databricks, Scala, Snowflake, Oracle, Data Modeling, Snowflake Schema, ELT, Git</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ff1351b933e73ff</t>
+          <t>https://www.indeed.com/viewjob?jk=06a961338cdff4c7</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET)</t>
+          <t>Data Modeling &amp; Data Governance Senior Consultant - Global Employer Services Technology</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Foodsmart</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
+          <t>Redshift, RDS, Databricks, Scala, Snowflake, Oracle, Data Modeling, Snowflake Schema, ELT, Git</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=547c7125b0b30619</t>
+          <t>https://www.indeed.com/viewjob?jk=5a8dc52df424a812</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET)</t>
+          <t>Data Modeling &amp; Data Governance Senior Consultant - Global Employer Services Technology</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Foodsmart</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
+          <t>Redshift, RDS, Databricks, Scala, Snowflake, Oracle, Data Modeling, Snowflake Schema, ELT, Git</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=364f3e4259c47f25</t>
+          <t>https://www.indeed.com/viewjob?jk=3e3d3e1280702eb1</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Modeling &amp; Data Governance Senior Consultant - Global Employer Services Technology</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Foodsmart</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, Airflow, Apache Airflow</t>
+          <t>Redshift, RDS, Databricks, Scala, Snowflake, Oracle, Data Modeling, Snowflake Schema, ELT, Git</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aaeba0c578886154</t>
+          <t>https://www.indeed.com/viewjob?jk=61ce98159d51d115</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Modeling &amp; Data Governance Senior Consultant - Global Employer Services Technology</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Foodsmart</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, Airflow, Apache Airflow</t>
+          <t>Redshift, RDS, Databricks, Scala, Snowflake, Oracle, Data Modeling, Snowflake Schema, ELT, Git</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c32c34ff06b9605</t>
+          <t>https://www.indeed.com/viewjob?jk=e949ea802386aee4</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Modeling &amp; Data Governance Senior Consultant - Global Employer Services Technology</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Foodsmart</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>West, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, Airflow, Apache Airflow</t>
+          <t>Redshift, RDS, Databricks, Scala, Snowflake, Oracle, Data Modeling, Snowflake Schema, ELT, Git</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c0f59a5cadbe7f1</t>
+          <t>https://www.indeed.com/viewjob?jk=89b2dfb0f97e69c0</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5bbdd9aeeabb621</t>
+          <t>https://www.indeed.com/viewjob?jk=5426946ff66f44cb</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c86ac4ab76e539c1</t>
+          <t>https://www.indeed.com/viewjob?jk=966efb03a4505663</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06a961338cdff4c7</t>
+          <t>https://www.indeed.com/viewjob?jk=9cd0270d6d2fdb49</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a8dc52df424a812</t>
+          <t>https://www.indeed.com/viewjob?jk=79d317ebbe4365ed</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e3d3e1280702eb1</t>
+          <t>https://www.indeed.com/viewjob?jk=aa85be0d893f7e04</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61ce98159d51d115</t>
+          <t>https://www.indeed.com/viewjob?jk=d0728d5f76d49bf4</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e949ea802386aee4</t>
+          <t>https://www.indeed.com/viewjob?jk=1336edda4057fc25</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89b2dfb0f97e69c0</t>
+          <t>https://www.indeed.com/viewjob?jk=793c1866762fa2ca</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5426946ff66f44cb</t>
+          <t>https://www.indeed.com/viewjob?jk=4df1d967651bceda</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=966efb03a4505663</t>
+          <t>https://www.indeed.com/viewjob?jk=8e3288bd3db664fa</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Modeling &amp; Data Governance Senior Consultant - Global Employer Services Technology</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, Scala, Snowflake, Oracle, Data Modeling, Snowflake Schema, ELT, Git</t>
+          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, Snowflake, ETL, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1475,356 +1475,6 @@
         </is>
       </c>
       <c r="G30" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9cd0270d6d2fdb49</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Data Modeling &amp; Data Governance Senior Consultant - Global Employer Services Technology</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Los Angeles, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Redshift, RDS, Databricks, Scala, Snowflake, Oracle, Data Modeling, Snowflake Schema, ELT, Git</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=79d317ebbe4365ed</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Data Modeling &amp; Data Governance Senior Consultant - Global Employer Services Technology</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Jersey City, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Redshift, RDS, Databricks, Scala, Snowflake, Oracle, Data Modeling, Snowflake Schema, ELT, Git</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=aa85be0d893f7e04</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Data Modeling &amp; Data Governance Senior Consultant - Global Employer Services Technology</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Redshift, RDS, Databricks, Scala, Snowflake, Oracle, Data Modeling, Snowflake Schema, ELT, Git</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d0728d5f76d49bf4</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Data Modeling &amp; Data Governance Senior Consultant - Global Employer Services Technology</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Tampa, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Redshift, RDS, Databricks, Scala, Snowflake, Oracle, Data Modeling, Snowflake Schema, ELT, Git</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1336edda4057fc25</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Data Modeling &amp; Data Governance Senior Consultant - Global Employer Services Technology</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Redshift, RDS, Databricks, Scala, Snowflake, Oracle, Data Modeling, Snowflake Schema, ELT, Git</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=793c1866762fa2ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Data Modeling &amp; Data Governance Senior Consultant - Global Employer Services Technology</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Redshift, RDS, Databricks, Scala, Snowflake, Oracle, Data Modeling, Snowflake Schema, ELT, Git</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4df1d967651bceda</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Data Modeling &amp; Data Governance Senior Consultant - Global Employer Services Technology</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Costa Mesa, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Redshift, RDS, Databricks, Scala, Snowflake, Oracle, Data Modeling, Snowflake Schema, ELT, Git</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8e3288bd3db664fa</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Bethesda, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b221a3fa0ea5bd27</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cc63a267293974cf</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>AI Application Architect</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, Snowflake, ETL, MLOps, MLflow, CI/CD</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=b57504d4cd793d31</t>
         </is>

--- a/results/job_matches_2026-05-03.xlsx
+++ b/results/job_matches_2026-05-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,7 +538,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer (GCP)</t>
+          <t>GCP Support Associate</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -552,11 +552,11 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16</v>
+        <v>13.2</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Azure, Google Cloud Platform, GCP, Kafka, NoSQL, Data Modeling, ETL, Talend, Tableau, Splunk</t>
+          <t>AWS, EMR, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,14 +566,14 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abcb767c36c64a35</t>
+          <t>https://www.indeed.com/viewjob?jk=0d636a662e603c9d</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Cloud AI Application Administrator</t>
+          <t>GCP Support Associate</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -587,11 +587,11 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.9</v>
+        <v>11.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, Azure, Scala, CI/CD, GitHub Actions, Terraform</t>
+          <t>ECS, IAM, Google Cloud Platform, GCP, Dataflow, Cloud Storage, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,14 +601,14 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18ebfd30511cd60d</t>
+          <t>https://www.indeed.com/viewjob?jk=1097e9f29f6e8b0a</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>GCP Support Associate</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -622,11 +622,11 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, EMR, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Snowflake</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, MLOps, MLflow, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,147 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d636a662e603c9d</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>GCP Support Associate</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>ECS, IAM, Google Cloud Platform, GCP, Dataflow, Cloud Storage, Jenkins, Terraform, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1097e9f29f6e8b0a</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Junior GCP Cloud Engineer</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>ECS, IAM, Google Cloud Platform, GCP, Dataflow, Cloud Storage, Jenkins, Terraform, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=08d4cd78d3dbe405</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>AI Application Architect</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, MLOps, MLflow, CI/CD, Jenkins, Docker</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=393116d7c03fb80f</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>AI Application Architect</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, Snowflake, ETL, MLOps, MLflow, CI/CD</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b57504d4cd793d31</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-05-03.xlsx
+++ b/results/job_matches_2026-05-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,35 +538,35 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>GCP Support Associate</t>
+          <t>Data Engineer (DataOps &amp; Infrastructure Focus)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Guidewire</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.2</v>
+        <v>16</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, EMR, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Snowflake</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, IAM, RDS, Spark, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d636a662e603c9d</t>
+          <t>https://www.indeed.com/viewjob?jk=6125421c57f16e3e</t>
         </is>
       </c>
     </row>
@@ -587,11 +587,11 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>ECS, IAM, Google Cloud Platform, GCP, Dataflow, Cloud Storage, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, EMR, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,14 +601,14 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1097e9f29f6e8b0a</t>
+          <t>https://www.indeed.com/viewjob?jk=0d636a662e603c9d</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>GCP Support Associate</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -626,15 +626,50 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
+          <t>ECS, IAM, Google Cloud Platform, GCP, Dataflow, Cloud Storage, Jenkins, Terraform, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1097e9f29f6e8b0a</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>AI Application Architect</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, MLOps, MLflow, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>2026-05-02</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=393116d7c03fb80f</t>
         </is>

--- a/results/job_matches_2026-05-03.xlsx
+++ b/results/job_matches_2026-05-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,35 +573,35 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>GCP Support Associate</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>The Cheesecake Factory</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Calabasas Hills, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, EMR, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, BigQuery, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d636a662e603c9d</t>
+          <t>https://www.indeed.com/viewjob?jk=aedebd419ff75231</t>
         </is>
       </c>
     </row>
@@ -622,11 +622,11 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>ECS, IAM, Google Cloud Platform, GCP, Dataflow, Cloud Storage, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, EMR, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,14 +636,14 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1097e9f29f6e8b0a</t>
+          <t>https://www.indeed.com/viewjob?jk=0d636a662e603c9d</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>GCP Support Associate</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -661,15 +661,50 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
+          <t>ECS, IAM, Google Cloud Platform, GCP, Dataflow, Cloud Storage, Jenkins, Terraform, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1097e9f29f6e8b0a</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>AI Application Architect</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, MLOps, MLflow, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>2026-05-02</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=393116d7c03fb80f</t>
         </is>

--- a/results/job_matches_2026-05-03.xlsx
+++ b/results/job_matches_2026-05-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>IDB Invest - Data Engineer (Sr Officer) Officer</t>
+          <t>Junior DevOps Engineer (GCP)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Inter-American Development Bank</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20.8</v>
+        <v>17.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables</t>
+          <t>AWS, SQS, SNS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,67 +496,67 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=975f0416f1286d47</t>
+          <t>https://www.indeed.com/viewjob?jk=8b84e2ec1da33ebd</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Junior DevOps Engineer (GCP)</t>
+          <t>Data Engineer (DataOps &amp; Infrastructure Focus)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Guidewire</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.4</v>
+        <v>16</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, IAM, RDS, Spark, Scala</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b84e2ec1da33ebd</t>
+          <t>https://www.indeed.com/viewjob?jk=6125421c57f16e3e</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer (DataOps &amp; Infrastructure Focus)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Guidewire</t>
+          <t>The Cheesecake Factory</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Calabasas Hills, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16</v>
+        <v>13.9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, IAM, RDS, Spark, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, BigQuery, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,42 +566,42 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6125421c57f16e3e</t>
+          <t>https://www.indeed.com/viewjob?jk=aedebd419ff75231</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>GCP Support Associate</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>The Cheesecake Factory</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Calabasas Hills, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, BigQuery, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, EMR, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aedebd419ff75231</t>
+          <t>https://www.indeed.com/viewjob?jk=0d636a662e603c9d</t>
         </is>
       </c>
     </row>
@@ -622,11 +622,11 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, EMR, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Snowflake</t>
+          <t>ECS, IAM, Google Cloud Platform, GCP, Dataflow, Cloud Storage, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,14 +636,14 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d636a662e603c9d</t>
+          <t>https://www.indeed.com/viewjob?jk=1097e9f29f6e8b0a</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>GCP Support Associate</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ECS, IAM, Google Cloud Platform, GCP, Dataflow, Cloud Storage, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, MLOps, MLflow, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -670,41 +670,6 @@
         </is>
       </c>
       <c r="G7" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1097e9f29f6e8b0a</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>AI Application Architect</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, MLOps, MLflow, CI/CD, Jenkins, Docker</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=393116d7c03fb80f</t>
         </is>

--- a/results/job_matches_2026-05-03.xlsx
+++ b/results/job_matches_2026-05-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Junior DevOps Engineer (GCP)</t>
+          <t>Data Engineer (DataOps &amp; Infrastructure Focus)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Guidewire</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>17.4</v>
+        <v>16</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, IAM, RDS, Spark, Scala</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b84e2ec1da33ebd</t>
+          <t>https://www.indeed.com/viewjob?jk=6125421c57f16e3e</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineer (DataOps &amp; Infrastructure Focus)</t>
+          <t>Solutions Architect - Cloud Data Warehousing (GCP)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Guidewire</t>
+          <t>Mattel, Inc.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>El Segundo, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, IAM, RDS, Spark, Scala</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,7 +531,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6125421c57f16e3e</t>
+          <t>https://www.indeed.com/viewjob?jk=54329e26a8f1201c</t>
         </is>
       </c>
     </row>
@@ -573,105 +573,35 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>GCP Support Associate</t>
+          <t>Sr. Engineer - Safety Analytics, Tools &amp; Databases</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, EMR, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Snowflake, Oracle, SQL Server, NoSQL, Power BI</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d636a662e603c9d</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>GCP Support Associate</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>ECS, IAM, Google Cloud Platform, GCP, Dataflow, Cloud Storage, Jenkins, Terraform, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1097e9f29f6e8b0a</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>AI Application Architect</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, MLOps, MLflow, CI/CD, Jenkins, Docker</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=393116d7c03fb80f</t>
+          <t>https://www.indeed.com/viewjob?jk=1310a0840225d1d5</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-05-03.xlsx
+++ b/results/job_matches_2026-05-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54329e26a8f1201c</t>
+          <t>https://www.indeed.com/viewjob?jk=8e22eed84f3a0e5a</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Solutions Architect - Cloud Data Warehousing (GCP)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>The Cheesecake Factory</t>
+          <t>Mattel, Inc.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Calabasas Hills, CA, US USA</t>
+          <t>El Segundo, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, BigQuery, Scala, Kafka, Snowflake, ETL</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,40 +566,75 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aedebd419ff75231</t>
+          <t>https://www.indeed.com/viewjob?jk=54329e26a8f1201c</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>The Cheesecake Factory</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Calabasas Hills, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, BigQuery, Scala, Kafka, Snowflake, ETL</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=aedebd419ff75231</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>Sr. Engineer - Safety Analytics, Tools &amp; Databases</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Arlington, VA, US USA</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="D6" t="n">
         <v>11.8</v>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>AWS, RDS, Azure, Databricks, GCP, Snowflake, Oracle, SQL Server, NoSQL, Power BI</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>2026-05-03</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=1310a0840225d1d5</t>
         </is>

--- a/results/job_matches_2026-05-03.xlsx
+++ b/results/job_matches_2026-05-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -637,6 +637,41 @@
       <c r="G6" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=1310a0840225d1d5</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>PHP Developer</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Scroll Tab</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Spark, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c010e703dc6247a2</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-05-03.xlsx
+++ b/results/job_matches_2026-05-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,6 +675,636 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Data Modeling &amp; Data Governance Senior Consultant - Global Employer Services Technology</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>San Antonio, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Redshift, RDS, Databricks, Scala, Snowflake, Oracle, Data Modeling, Snowflake Schema, ELT, Git</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b5bbdd9aeeabb621</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Data Modeling &amp; Data Governance Senior Consultant - Global Employer Services Technology</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Redshift, RDS, Databricks, Scala, Snowflake, Oracle, Data Modeling, Snowflake Schema, ELT, Git</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c86ac4ab76e539c1</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Data Modeling &amp; Data Governance Senior Consultant - Global Employer Services Technology</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Redshift, RDS, Databricks, Scala, Snowflake, Oracle, Data Modeling, Snowflake Schema, ELT, Git</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=06a961338cdff4c7</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Data Modeling &amp; Data Governance Senior Consultant - Global Employer Services Technology</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Redshift, RDS, Databricks, Scala, Snowflake, Oracle, Data Modeling, Snowflake Schema, ELT, Git</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5a8dc52df424a812</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Data Modeling &amp; Data Governance Senior Consultant - Global Employer Services Technology</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Redshift, RDS, Databricks, Scala, Snowflake, Oracle, Data Modeling, Snowflake Schema, ELT, Git</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3e3d3e1280702eb1</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Data Modeling &amp; Data Governance Senior Consultant - Global Employer Services Technology</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Morristown, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Redshift, RDS, Databricks, Scala, Snowflake, Oracle, Data Modeling, Snowflake Schema, ELT, Git</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=61ce98159d51d115</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Data Modeling &amp; Data Governance Senior Consultant - Global Employer Services Technology</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Redshift, RDS, Databricks, Scala, Snowflake, Oracle, Data Modeling, Snowflake Schema, ELT, Git</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e949ea802386aee4</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Data Modeling &amp; Data Governance Senior Consultant - Global Employer Services Technology</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Redshift, RDS, Databricks, Scala, Snowflake, Oracle, Data Modeling, Snowflake Schema, ELT, Git</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=89b2dfb0f97e69c0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Data Modeling &amp; Data Governance Senior Consultant - Global Employer Services Technology</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Jacksonville, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Redshift, RDS, Databricks, Scala, Snowflake, Oracle, Data Modeling, Snowflake Schema, ELT, Git</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5426946ff66f44cb</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Data Modeling &amp; Data Governance Senior Consultant - Global Employer Services Technology</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>San Diego, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Redshift, RDS, Databricks, Scala, Snowflake, Oracle, Data Modeling, Snowflake Schema, ELT, Git</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=966efb03a4505663</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Data Modeling &amp; Data Governance Senior Consultant - Global Employer Services Technology</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Redshift, RDS, Databricks, Scala, Snowflake, Oracle, Data Modeling, Snowflake Schema, ELT, Git</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9cd0270d6d2fdb49</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Data Modeling &amp; Data Governance Senior Consultant - Global Employer Services Technology</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Redshift, RDS, Databricks, Scala, Snowflake, Oracle, Data Modeling, Snowflake Schema, ELT, Git</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=79d317ebbe4365ed</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Data Modeling &amp; Data Governance Senior Consultant - Global Employer Services Technology</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Jersey City, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Redshift, RDS, Databricks, Scala, Snowflake, Oracle, Data Modeling, Snowflake Schema, ELT, Git</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=aa85be0d893f7e04</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Data Modeling &amp; Data Governance Senior Consultant - Global Employer Services Technology</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Redshift, RDS, Databricks, Scala, Snowflake, Oracle, Data Modeling, Snowflake Schema, ELT, Git</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d0728d5f76d49bf4</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Data Modeling &amp; Data Governance Senior Consultant - Global Employer Services Technology</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Redshift, RDS, Databricks, Scala, Snowflake, Oracle, Data Modeling, Snowflake Schema, ELT, Git</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1336edda4057fc25</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Data Modeling &amp; Data Governance Senior Consultant - Global Employer Services Technology</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Redshift, RDS, Databricks, Scala, Snowflake, Oracle, Data Modeling, Snowflake Schema, ELT, Git</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=793c1866762fa2ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Data Modeling &amp; Data Governance Senior Consultant - Global Employer Services Technology</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Redshift, RDS, Databricks, Scala, Snowflake, Oracle, Data Modeling, Snowflake Schema, ELT, Git</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4df1d967651bceda</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Data Modeling &amp; Data Governance Senior Consultant - Global Employer Services Technology</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Costa Mesa, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Redshift, RDS, Databricks, Scala, Snowflake, Oracle, Data Modeling, Snowflake Schema, ELT, Git</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8e3288bd3db664fa</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/results/job_matches_2026-05-03.xlsx
+++ b/results/job_matches_2026-05-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,636 +672,6 @@
       <c r="G7" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=c010e703dc6247a2</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Data Modeling &amp; Data Governance Senior Consultant - Global Employer Services Technology</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>San Antonio, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Redshift, RDS, Databricks, Scala, Snowflake, Oracle, Data Modeling, Snowflake Schema, ELT, Git</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b5bbdd9aeeabb621</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Data Modeling &amp; Data Governance Senior Consultant - Global Employer Services Technology</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Redshift, RDS, Databricks, Scala, Snowflake, Oracle, Data Modeling, Snowflake Schema, ELT, Git</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c86ac4ab76e539c1</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Data Modeling &amp; Data Governance Senior Consultant - Global Employer Services Technology</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Redshift, RDS, Databricks, Scala, Snowflake, Oracle, Data Modeling, Snowflake Schema, ELT, Git</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=06a961338cdff4c7</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Data Modeling &amp; Data Governance Senior Consultant - Global Employer Services Technology</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Redshift, RDS, Databricks, Scala, Snowflake, Oracle, Data Modeling, Snowflake Schema, ELT, Git</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5a8dc52df424a812</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Data Modeling &amp; Data Governance Senior Consultant - Global Employer Services Technology</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Redshift, RDS, Databricks, Scala, Snowflake, Oracle, Data Modeling, Snowflake Schema, ELT, Git</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3e3d3e1280702eb1</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Data Modeling &amp; Data Governance Senior Consultant - Global Employer Services Technology</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Morristown, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Redshift, RDS, Databricks, Scala, Snowflake, Oracle, Data Modeling, Snowflake Schema, ELT, Git</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=61ce98159d51d115</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Data Modeling &amp; Data Governance Senior Consultant - Global Employer Services Technology</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Redshift, RDS, Databricks, Scala, Snowflake, Oracle, Data Modeling, Snowflake Schema, ELT, Git</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e949ea802386aee4</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Data Modeling &amp; Data Governance Senior Consultant - Global Employer Services Technology</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>San Jose, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Redshift, RDS, Databricks, Scala, Snowflake, Oracle, Data Modeling, Snowflake Schema, ELT, Git</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=89b2dfb0f97e69c0</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Data Modeling &amp; Data Governance Senior Consultant - Global Employer Services Technology</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Jacksonville, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Redshift, RDS, Databricks, Scala, Snowflake, Oracle, Data Modeling, Snowflake Schema, ELT, Git</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5426946ff66f44cb</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Data Modeling &amp; Data Governance Senior Consultant - Global Employer Services Technology</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>San Diego, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Redshift, RDS, Databricks, Scala, Snowflake, Oracle, Data Modeling, Snowflake Schema, ELT, Git</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=966efb03a4505663</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Data Modeling &amp; Data Governance Senior Consultant - Global Employer Services Technology</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Redshift, RDS, Databricks, Scala, Snowflake, Oracle, Data Modeling, Snowflake Schema, ELT, Git</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9cd0270d6d2fdb49</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Data Modeling &amp; Data Governance Senior Consultant - Global Employer Services Technology</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Los Angeles, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Redshift, RDS, Databricks, Scala, Snowflake, Oracle, Data Modeling, Snowflake Schema, ELT, Git</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=79d317ebbe4365ed</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Data Modeling &amp; Data Governance Senior Consultant - Global Employer Services Technology</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Jersey City, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Redshift, RDS, Databricks, Scala, Snowflake, Oracle, Data Modeling, Snowflake Schema, ELT, Git</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=aa85be0d893f7e04</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Data Modeling &amp; Data Governance Senior Consultant - Global Employer Services Technology</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Redshift, RDS, Databricks, Scala, Snowflake, Oracle, Data Modeling, Snowflake Schema, ELT, Git</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d0728d5f76d49bf4</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Data Modeling &amp; Data Governance Senior Consultant - Global Employer Services Technology</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Tampa, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Redshift, RDS, Databricks, Scala, Snowflake, Oracle, Data Modeling, Snowflake Schema, ELT, Git</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1336edda4057fc25</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Data Modeling &amp; Data Governance Senior Consultant - Global Employer Services Technology</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Redshift, RDS, Databricks, Scala, Snowflake, Oracle, Data Modeling, Snowflake Schema, ELT, Git</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=793c1866762fa2ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Data Modeling &amp; Data Governance Senior Consultant - Global Employer Services Technology</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Redshift, RDS, Databricks, Scala, Snowflake, Oracle, Data Modeling, Snowflake Schema, ELT, Git</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4df1d967651bceda</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Data Modeling &amp; Data Governance Senior Consultant - Global Employer Services Technology</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Costa Mesa, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Redshift, RDS, Databricks, Scala, Snowflake, Oracle, Data Modeling, Snowflake Schema, ELT, Git</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8e3288bd3db664fa</t>
         </is>
       </c>
     </row>
